--- a/Risk_Register.xlsx.xlsx
+++ b/Risk_Register.xlsx.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="63">
   <si>
     <t>Risk ID</t>
   </si>
@@ -36,10 +36,175 @@
     <t>Risk level</t>
   </si>
   <si>
-    <t>Treatment</t>
-  </si>
-  <si>
-    <t>Vulnurabiility</t>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>Customer database</t>
+  </si>
+  <si>
+    <t>Data breach</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>Payment processing system</t>
+  </si>
+  <si>
+    <t>Unauthorized access</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employee workstations </t>
+  </si>
+  <si>
+    <t>Malware infections</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>Employee accounts</t>
+  </si>
+  <si>
+    <t>Phishing</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>Cloud infracstructure</t>
+  </si>
+  <si>
+    <t>Cloud misconfiguration</t>
+  </si>
+  <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>Internal systems</t>
+  </si>
+  <si>
+    <t>Insider threats</t>
+  </si>
+  <si>
+    <t>R7</t>
+  </si>
+  <si>
+    <t>Payment platform</t>
+  </si>
+  <si>
+    <t>DDoS attack</t>
+  </si>
+  <si>
+    <t>R8</t>
+  </si>
+  <si>
+    <t>Organizational systems</t>
+  </si>
+  <si>
+    <t>Ransomware</t>
+  </si>
+  <si>
+    <t>R9</t>
+  </si>
+  <si>
+    <t>Credential thefts</t>
+  </si>
+  <si>
+    <t>R10</t>
+  </si>
+  <si>
+    <t>Internal infracstructure</t>
+  </si>
+  <si>
+    <t>System failure</t>
+  </si>
+  <si>
+    <t>Vulnerabiility</t>
+  </si>
+  <si>
+    <t>Weak access controls</t>
+  </si>
+  <si>
+    <t>No MFA</t>
+  </si>
+  <si>
+    <t>Outdated antivirus</t>
+  </si>
+  <si>
+    <t>Lack of awareness training</t>
+  </si>
+  <si>
+    <t>Misconfigured storage</t>
+  </si>
+  <si>
+    <t>Excessive priviledges</t>
+  </si>
+  <si>
+    <t>Lack of network monitoring</t>
+  </si>
+  <si>
+    <t>Lack of backups</t>
+  </si>
+  <si>
+    <t>Weak password policy</t>
+  </si>
+  <si>
+    <t>No redundant systems</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low </t>
+  </si>
+  <si>
+    <t>Treatment strategy</t>
+  </si>
+  <si>
+    <t>Mitigate</t>
+  </si>
+  <si>
+    <t>Recommended controls</t>
+  </si>
+  <si>
+    <t>Implement role-based access control and regular access reviews</t>
+  </si>
+  <si>
+    <t>Implement multi-factor authentication</t>
+  </si>
+  <si>
+    <t>Deploy endpoint protection and automatic security updates</t>
+  </si>
+  <si>
+    <t>Conduct regular security awareness training</t>
+  </si>
+  <si>
+    <t>Implement cloud security monitoring and configuration audits</t>
+  </si>
+  <si>
+    <t>Apply least privilege access and monitor user activity</t>
+  </si>
+  <si>
+    <t>Deploy network traffic monitoring and DDoS protection services</t>
+  </si>
+  <si>
+    <t>Implement regular data backups and recovery procedures</t>
+  </si>
+  <si>
+    <t>Enforce strong password policies and password management tools</t>
+  </si>
+  <si>
+    <t>Implement system redundancy and disaster recovery planning</t>
   </si>
 </sst>
 </file>
@@ -75,8 +240,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -87,17 +256,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:H2" insertRow="1" totalsRowShown="0">
-  <autoFilter ref="A1:H2"/>
-  <tableColumns count="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:I11" totalsRowShown="0">
+  <autoFilter ref="A1:I11">
+    <filterColumn colId="8"/>
+  </autoFilter>
+  <tableColumns count="9">
     <tableColumn id="1" name="Risk ID"/>
     <tableColumn id="2" name="Asset"/>
     <tableColumn id="3" name="Threat"/>
-    <tableColumn id="4" name="Vulnurabiility"/>
+    <tableColumn id="4" name="Vulnerabiility"/>
     <tableColumn id="5" name="Likelihood"/>
     <tableColumn id="6" name="Impact"/>
     <tableColumn id="7" name="Risk level"/>
-    <tableColumn id="8" name="Treatment"/>
+    <tableColumn id="8" name="Treatment strategy"/>
+    <tableColumn id="9" name="Recommended controls"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -388,19 +560,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" customWidth="1"/>
+    <col min="4" max="4" width="24.42578125" customWidth="1"/>
     <col min="5" max="5" width="13.28515625" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="12.5703125" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" customWidth="1"/>
+    <col min="9" max="9" width="60.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -411,7 +585,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -423,7 +597,300 @@
         <v>5</v>
       </c>
       <c r="H1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
         <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="30">
+      <c r="A10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
